--- a/raw_data/AU/AfricanUnion_n_55_subregions.xlsx
+++ b/raw_data/AU/AfricanUnion_n_55_subregions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unicef.sharepoint.com/teams/DAPM-ChildMortality/Shared Documents/UN IGME data/update country.info.CME/Country-and-Region-Metadata/raw_data/African Union/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unicef.sharepoint.com/teams/DAPM-ChildMortality/Shared Documents/UN IGME data/update country.info.CME/Country-and-Region-Metadata/raw_data/AU/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{014FE85F-0A5C-4CF2-9817-A894800472BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{014FE85F-0A5C-4CF2-9817-A894800472BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E77935E5-0321-4D66-832E-9557EBDE7484}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -407,12 +407,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -427,8 +433,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -755,513 +762,513 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D2" t="str">
-        <f t="shared" ref="D2:D33" si="0">RIGHT(C2,LEN(C2)-FIND("_",C2))</f>
-        <v>Southern Africa</v>
+      <c r="A2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <f>RIGHT(C2,LEN(C2)-FIND("_",C2))</f>
+        <v>Central Africa</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D3" t="str">
-        <f t="shared" si="0"/>
+      <c r="D3" s="1" t="str">
+        <f>RIGHT(C3,LEN(C3)-FIND("_",C3))</f>
         <v>Central Africa</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D4" t="str">
-        <f t="shared" si="0"/>
-        <v>Western Africa</v>
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" s="1" t="str">
+        <f>RIGHT(C4,LEN(C4)-FIND("_",C4))</f>
+        <v>Central Africa</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D5" t="str">
-        <f t="shared" si="0"/>
-        <v>Western Africa</v>
+      <c r="A5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" s="1" t="str">
+        <f>RIGHT(C5,LEN(C5)-FIND("_",C5))</f>
+        <v>Central Africa</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" t="str">
-        <f t="shared" si="0"/>
-        <v>Southern Africa</v>
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="1" t="str">
+        <f>RIGHT(C6,LEN(C6)-FIND("_",C6))</f>
+        <v>Central Africa</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D7" t="str">
-        <f t="shared" si="0"/>
+      <c r="D7" s="1" t="str">
+        <f>RIGHT(C7,LEN(C7)-FIND("_",C7))</f>
         <v>Central Africa</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" t="s">
-        <v>117</v>
-      </c>
-      <c r="D8" t="str">
-        <f t="shared" si="0"/>
-        <v>Western Africa</v>
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="1" t="str">
+        <f>RIGHT(C8,LEN(C8)-FIND("_",C8))</f>
+        <v>Central Africa</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="A9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D9" t="str">
-        <f t="shared" si="0"/>
+      <c r="D9" s="1" t="str">
+        <f>RIGHT(C9,LEN(C9)-FIND("_",C9))</f>
         <v>Central Africa</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D10" t="str">
-        <f t="shared" si="0"/>
+      <c r="D10" s="1" t="str">
+        <f>RIGHT(C10,LEN(C10)-FIND("_",C10))</f>
         <v>Central Africa</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D11" t="str">
-        <f t="shared" si="0"/>
-        <v>Central Africa</v>
+        <f>RIGHT(C11,LEN(C11)-FIND("_",C11))</f>
+        <v>Eastern Africa</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
         <v>114</v>
       </c>
       <c r="D12" t="str">
-        <f t="shared" si="0"/>
+        <f>RIGHT(C12,LEN(C12)-FIND("_",C12))</f>
         <v>Eastern Africa</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D13" t="str">
-        <f t="shared" si="0"/>
-        <v>Western Africa</v>
+        <f>RIGHT(C13,LEN(C13)-FIND("_",C13))</f>
+        <v>Eastern Africa</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
         <v>114</v>
       </c>
       <c r="D14" t="str">
-        <f t="shared" si="0"/>
+        <f>RIGHT(C14,LEN(C14)-FIND("_",C14))</f>
         <v>Eastern Africa</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D15" t="str">
-        <f t="shared" si="0"/>
-        <v>Northern Africa</v>
+        <f>RIGHT(C15,LEN(C15)-FIND("_",C15))</f>
+        <v>Eastern Africa</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D16" t="str">
-        <f t="shared" si="0"/>
-        <v>Northern Africa</v>
+        <f>RIGHT(C16,LEN(C16)-FIND("_",C16))</f>
+        <v>Eastern Africa</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
         <v>114</v>
       </c>
       <c r="D17" t="str">
-        <f t="shared" si="0"/>
+        <f>RIGHT(C17,LEN(C17)-FIND("_",C17))</f>
         <v>Eastern Africa</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>111</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D18" t="str">
-        <f t="shared" si="0"/>
-        <v>Northern Africa</v>
+        <f>RIGHT(C18,LEN(C18)-FIND("_",C18))</f>
+        <v>Eastern Africa</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
         <v>114</v>
       </c>
       <c r="D19" t="str">
-        <f t="shared" si="0"/>
+        <f>RIGHT(C19,LEN(C19)-FIND("_",C19))</f>
         <v>Eastern Africa</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D20" t="str">
-        <f t="shared" si="0"/>
-        <v>Central Africa</v>
+        <f>RIGHT(C20,LEN(C20)-FIND("_",C20))</f>
+        <v>Eastern Africa</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D21" t="str">
-        <f t="shared" si="0"/>
-        <v>Western Africa</v>
+        <f>RIGHT(C21,LEN(C21)-FIND("_",C21))</f>
+        <v>Eastern Africa</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D22" t="str">
-        <f t="shared" si="0"/>
-        <v>Western Africa</v>
+        <f>RIGHT(C22,LEN(C22)-FIND("_",C22))</f>
+        <v>Eastern Africa</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D23" t="str">
-        <f t="shared" si="0"/>
-        <v>Western Africa</v>
+        <f>RIGHT(C23,LEN(C23)-FIND("_",C23))</f>
+        <v>Eastern Africa</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D24" t="str">
-        <f t="shared" si="0"/>
-        <v>Western Africa</v>
+        <f>RIGHT(C24,LEN(C24)-FIND("_",C24))</f>
+        <v>Eastern Africa</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" t="s">
-        <v>113</v>
-      </c>
-      <c r="D25" t="str">
-        <f t="shared" si="0"/>
-        <v>Central Africa</v>
+      <c r="A25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" s="1" t="str">
+        <f>RIGHT(C25,LEN(C25)-FIND("_",C25))</f>
+        <v>Northern Africa</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" t="s">
-        <v>114</v>
-      </c>
-      <c r="D26" t="str">
-        <f t="shared" si="0"/>
-        <v>Eastern Africa</v>
+      <c r="A26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26" s="1" t="str">
+        <f>RIGHT(C26,LEN(C26)-FIND("_",C26))</f>
+        <v>Northern Africa</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C27" t="s">
-        <v>117</v>
-      </c>
-      <c r="D27" t="str">
-        <f t="shared" si="0"/>
-        <v>Western Africa</v>
+      <c r="A27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D27" s="1" t="str">
+        <f>RIGHT(C27,LEN(C27)-FIND("_",C27))</f>
+        <v>Northern Africa</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="A28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D28" t="str">
-        <f t="shared" si="0"/>
+      <c r="D28" s="1" t="str">
+        <f>RIGHT(C28,LEN(C28)-FIND("_",C28))</f>
         <v>Northern Africa</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D29" t="str">
-        <f t="shared" si="0"/>
-        <v>Southern Africa</v>
+      <c r="A29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" s="1" t="str">
+        <f>RIGHT(C29,LEN(C29)-FIND("_",C29))</f>
+        <v>Northern Africa</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="A30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D30" t="str">
-        <f t="shared" si="0"/>
+      <c r="D30" s="1" t="str">
+        <f>RIGHT(C30,LEN(C30)-FIND("_",C30))</f>
         <v>Northern Africa</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" t="s">
-        <v>114</v>
-      </c>
-      <c r="D31" t="str">
-        <f t="shared" si="0"/>
-        <v>Eastern Africa</v>
+      <c r="A31" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D31" s="1" t="str">
+        <f>RIGHT(C31,LEN(C31)-FIND("_",C31))</f>
+        <v>Northern Africa</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D32" t="str">
-        <f t="shared" si="0"/>
-        <v>Western Africa</v>
+        <f>RIGHT(C32,LEN(C32)-FIND("_",C32))</f>
+        <v>Southern Africa</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s">
         <v>116</v>
       </c>
       <c r="D33" t="str">
-        <f t="shared" si="0"/>
+        <f>RIGHT(C33,LEN(C33)-FIND("_",C33))</f>
         <v>Southern Africa</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="C34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D34" t="str">
-        <f t="shared" ref="D34:D65" si="1">RIGHT(C34,LEN(C34)-FIND("_",C34))</f>
-        <v>Northern Africa</v>
+        <f>RIGHT(C34,LEN(C34)-FIND("_",C34))</f>
+        <v>Southern Africa</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C35" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D35" t="str">
-        <f t="shared" si="1"/>
-        <v>Eastern Africa</v>
+        <f>RIGHT(C35,LEN(C35)-FIND("_",C35))</f>
+        <v>Southern Africa</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1275,314 +1282,314 @@
         <v>116</v>
       </c>
       <c r="D36" t="str">
-        <f t="shared" si="1"/>
+        <f>RIGHT(C36,LEN(C36)-FIND("_",C36))</f>
         <v>Southern Africa</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C37" t="s">
         <v>116</v>
       </c>
       <c r="D37" t="str">
-        <f t="shared" si="1"/>
+        <f>RIGHT(C37,LEN(C37)-FIND("_",C37))</f>
         <v>Southern Africa</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="C38" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D38" t="str">
-        <f t="shared" si="1"/>
-        <v>Western Africa</v>
+        <f>RIGHT(C38,LEN(C38)-FIND("_",C38))</f>
+        <v>Southern Africa</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="C39" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D39" t="str">
-        <f t="shared" si="1"/>
-        <v>Western Africa</v>
+        <f>RIGHT(C39,LEN(C39)-FIND("_",C39))</f>
+        <v>Southern Africa</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C40" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D40" t="str">
-        <f t="shared" si="1"/>
-        <v>Eastern Africa</v>
+        <f>RIGHT(C40,LEN(C40)-FIND("_",C40))</f>
+        <v>Southern Africa</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="C41" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D41" t="str">
-        <f t="shared" si="1"/>
-        <v>Eastern Africa</v>
+        <f>RIGHT(C41,LEN(C41)-FIND("_",C41))</f>
+        <v>Southern Africa</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
         <v>117</v>
       </c>
       <c r="D42" t="str">
-        <f t="shared" si="1"/>
+        <f>RIGHT(C42,LEN(C42)-FIND("_",C42))</f>
         <v>Western Africa</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C43" t="s">
         <v>117</v>
       </c>
       <c r="D43" t="str">
-        <f t="shared" si="1"/>
+        <f>RIGHT(C43,LEN(C43)-FIND("_",C43))</f>
         <v>Western Africa</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D44" t="str">
-        <f t="shared" si="1"/>
-        <v>Eastern Africa</v>
+        <f>RIGHT(C44,LEN(C44)-FIND("_",C44))</f>
+        <v>Western Africa</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="C45" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D45" t="str">
-        <f t="shared" si="1"/>
-        <v>Eastern Africa</v>
+        <f>RIGHT(C45,LEN(C45)-FIND("_",C45))</f>
+        <v>Western Africa</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="C46" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D46" t="str">
-        <f t="shared" si="1"/>
-        <v>Central Africa</v>
+        <f>RIGHT(C46,LEN(C46)-FIND("_",C46))</f>
+        <v>Western Africa</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C47" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D47" t="str">
-        <f t="shared" si="1"/>
-        <v>Southern Africa</v>
+        <f>RIGHT(C47,LEN(C47)-FIND("_",C47))</f>
+        <v>Western Africa</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C48" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D48" t="str">
-        <f t="shared" si="1"/>
-        <v>Eastern Africa</v>
+        <f>RIGHT(C48,LEN(C48)-FIND("_",C48))</f>
+        <v>Western Africa</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="C49" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D49" t="str">
-        <f t="shared" si="1"/>
-        <v>Central Africa</v>
+        <f>RIGHT(C49,LEN(C49)-FIND("_",C49))</f>
+        <v>Western Africa</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C50" t="s">
         <v>117</v>
       </c>
       <c r="D50" t="str">
-        <f t="shared" si="1"/>
+        <f>RIGHT(C50,LEN(C50)-FIND("_",C50))</f>
         <v>Western Africa</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C51" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D51" t="str">
-        <f t="shared" si="1"/>
-        <v>Northern Africa</v>
+        <f>RIGHT(C51,LEN(C51)-FIND("_",C51))</f>
+        <v>Western Africa</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C52" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D52" t="str">
-        <f t="shared" si="1"/>
-        <v>Eastern Africa</v>
+        <f>RIGHT(C52,LEN(C52)-FIND("_",C52))</f>
+        <v>Western Africa</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="C53" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D53" t="str">
-        <f t="shared" si="1"/>
-        <v>Eastern Africa</v>
+        <f>RIGHT(C53,LEN(C53)-FIND("_",C53))</f>
+        <v>Western Africa</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C54" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D54" t="str">
-        <f t="shared" si="1"/>
-        <v>Southern Africa</v>
+        <f>RIGHT(C54,LEN(C54)-FIND("_",C54))</f>
+        <v>Western Africa</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="C55" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D55" t="str">
-        <f t="shared" si="1"/>
-        <v>Southern Africa</v>
+        <f>RIGHT(C55,LEN(C55)-FIND("_",C55))</f>
+        <v>Western Africa</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="C56" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D56" t="str">
-        <f t="shared" si="1"/>
-        <v>Southern Africa</v>
+        <f>RIGHT(C56,LEN(C56)-FIND("_",C56))</f>
+        <v>Western Africa</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D56">
-      <sortCondition ref="A1"/>
+      <sortCondition ref="C1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1609,8 +1616,83 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100136DC1853B882B4A8BB14DB670B2A2D3" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c683f7be9f0d396716ce49390aa9eada">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="37893236-cb76-4d6f-8a18-4c624154e39c" xmlns:ns3="f8563a7a-d9fa-431f-b50c-34632ce7e22e" xmlns:ns4="ca283e0b-db31-4043-a2ef-b80661bf084a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6535429bee677a8fa0693d9ffe697f6b" ns2:_="" ns3:_="" ns4:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f8563a7a-d9fa-431f-b50c-34632ce7e22e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ca283e0b-db31-4043-a2ef-b80661bf084a" xsi:nil="true"/>
+    <_dlc_DocId xmlns="37893236-cb76-4d6f-8a18-4c624154e39c">RFF2MQFYXHK7-870072624-107513</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="37893236-cb76-4d6f-8a18-4c624154e39c">
+      <Url>https://unicef.sharepoint.com/teams/DAPM-ChildMortality/_layouts/15/DocIdRedir.aspx?ID=RFF2MQFYXHK7-870072624-107513</Url>
+      <Description>RFF2MQFYXHK7-870072624-107513</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100136DC1853B882B4A8BB14DB670B2A2D3" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f28e78ef6e4f0f2a2a2482d8db47776a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="37893236-cb76-4d6f-8a18-4c624154e39c" xmlns:ns3="f8563a7a-d9fa-431f-b50c-34632ce7e22e" xmlns:ns4="ca283e0b-db31-4043-a2ef-b80661bf084a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f3f994f0b4e3408e34fd8b168c2d4f01" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="37893236-cb76-4d6f-8a18-4c624154e39c"/>
     <xsd:import namespace="f8563a7a-d9fa-431f-b50c-34632ce7e22e"/>
     <xsd:import namespace="ca283e0b-db31-4043-a2ef-b80661bf084a"/>
@@ -1639,6 +1721,7 @@
                 <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1772,6 +1855,11 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="28" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ca283e0b-db31-4043-a2ef-b80661bf084a" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -1887,93 +1975,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f8563a7a-d9fa-431f-b50c-34632ce7e22e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ca283e0b-db31-4043-a2ef-b80661bf084a" xsi:nil="true"/>
-    <_dlc_DocId xmlns="37893236-cb76-4d6f-8a18-4c624154e39c">RFF2MQFYXHK7-870072624-107513</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="37893236-cb76-4d6f-8a18-4c624154e39c">
-      <Url>https://unicef.sharepoint.com/teams/DAPM-ChildMortality/_layouts/15/DocIdRedir.aspx?ID=RFF2MQFYXHK7-870072624-107513</Url>
-      <Description>RFF2MQFYXHK7-870072624-107513</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61053087-F134-4981-85F8-F9FC6CF2DF02}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C80F969D-3B2C-47CA-999E-B98CD3C083B7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f8563a7a-d9fa-431f-b50c-34632ce7e22e"/>
+    <ds:schemaRef ds:uri="ca283e0b-db31-4043-a2ef-b80661bf084a"/>
+    <ds:schemaRef ds:uri="37893236-cb76-4d6f-8a18-4c624154e39c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F17EB84-3012-46D5-92EA-E2E53959E4BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93BE1DFA-EE38-4FD0-81B1-AE1CD4CFB9D9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93BE1DFA-EE38-4FD0-81B1-AE1CD4CFB9D9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F17EB84-3012-46D5-92EA-E2E53959E4BC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C80F969D-3B2C-47CA-999E-B98CD3C083B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{047A2665-F592-4B26-B0AC-006D42EC6AE7}"/>
 </file>